--- a/fournisseurs.xlsx
+++ b/fournisseurs.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\JOEL\Documents\python projects\intermediaire\Gestock App2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6180860-19D6-4A79-82AB-BD9D26C0F5FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61020D61-E220-43FB-BDEA-C85592894550}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{9694AAEE-F939-464A-A41E-FD9B7A463967}"/>
   </bookViews>
@@ -34,9 +34,6 @@
     <t>nom_fournisseur</t>
   </si>
   <si>
-    <t>ville</t>
-  </si>
-  <si>
     <t>OPTOPOL</t>
   </si>
   <si>
@@ -83,6 +80,9 @@
   </si>
   <si>
     <t>ITALIE</t>
+  </si>
+  <si>
+    <t>adresse</t>
   </si>
 </sst>
 </file>
@@ -460,71 +460,71 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -542,47 +542,47 @@
   <sheetData>
     <row r="1" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D2" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D3" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D4" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D6" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D7" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D8" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="4:4" x14ac:dyDescent="0.35">
       <c r="D9" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
